--- a/XBRL-template-MPERS/backup-originals/Group/10-SoRE.xlsx
+++ b/XBRL-template-MPERS/backup-originals/Group/10-SoRE.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -470,163 +470,128 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure of retained earnings [abstract]</t>
+          <t>Disclosure of retained earnings</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement of retained earnings [text block]</t>
+          <t>Statement of retained earnings</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of retained earnings [abstract]</t>
+          <t>Statement of retained earnings</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Disclosure of retained earnings [table]</t>
+          <t>Statement of retained earnings</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Retained earnings at beginning of period</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Impact of changes in accounting policies</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Retained earnings at beginning of period, restated</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Disclosure of retained earnings [line items]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Statement of retained earnings [abstract]</t>
+          <t>Profit (loss)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Retained earnings at beginning of period</t>
-        </is>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>*Total Profit (loss)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>1*B11</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>1*C11</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>1*D11</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>1*E11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Impact of changes in accounting policies</t>
+          <t>Changes in retained earnings</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Retained earnings at beginning of period, restated</t>
+          <t>Dividends paid</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Profit (loss) [abstract]</t>
-        </is>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>*Total increase (decrease) in retained earnings</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>1*B12+-1*B14</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>1*C12+-1*C14</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>1*D12+-1*D14</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>1*E12+-1*E14</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
-        <is>
-          <t>Profit (loss)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>*Total Profit (loss)</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>1*B16</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>1*C16</f>
-        <v/>
-      </c>
-      <c r="D17">
-        <f>1*D16</f>
-        <v/>
-      </c>
-      <c r="E17">
-        <f>1*E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Changes in retained earnings [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>*Total increase (decrease) in retained earnings</t>
-        </is>
-      </c>
-      <c r="B20">
-        <f>1*B17+-1*B19</f>
-        <v/>
-      </c>
-      <c r="C20">
-        <f>1*C17+-1*C19</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>1*D17+-1*D19</f>
-        <v/>
-      </c>
-      <c r="E20">
-        <f>1*E17+-1*E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
         <is>
           <t>Retained earnings at end of period</t>
         </is>
